--- a/scratch/input-ex1/comparisons-A.xlsx
+++ b/scratch/input-ex1/comparisons-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanmaygandhi/Box Sync/runModac/scratch/input-ex1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanmaygandhi/Box/runModac/scratch/input-ex1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9191535D-6BDD-6F48-B861-B3B98F90B7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE604C4-33F6-7344-B42C-964CC6E2BCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29240" yWindow="2860" windowWidth="19720" windowHeight="17720" activeTab="1" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="6" r:id="rId1"/>
@@ -756,7 +756,7 @@
         <v>68</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
